--- a/extenbooks/S802_extenbook.xlsx
+++ b/extenbooks/S802_extenbook.xlsx
@@ -1040,7 +1040,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -2157,11 +2157,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2184,76 +2184,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Share of Price Increases by Concentration, NBER Contractions (Semmler/Weston)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S802_research.json", "adequacy_report": "Technical/docs/chapters/CH8_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S802_DPR.md", "epr": "Technical/docs/series/S802_EPR.md", "loader": "Technical/code/L01_loaders/L01_S802_load.py", "processor": "Technical/code/P02_processors/P02_S802_construct.py", "validator": "Technical/code/V03_validators/V03_S802_validate.py", "processed": "Technical/data/processed/S802.parquet", "chopped_csv": "Technical/chopped/S802.csv", "extenbook_xlsx": "Technical/extenbooks/S802_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-19T00:22:18.990557+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S802_extenbook.xlsx
+++ b/extenbooks/S802_extenbook.xlsx
@@ -1054,7 +1054,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch8-fanout</t>
+          <t>**Author**: Anu automated extraction pipeline</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>`content_type = cross_sectional`: each contraction is its own industry cross-section binned by CR4 midpoint; the three contractions are not a continuous time index. Per the playbook recipe:</t>
+          <t>`content_type = cross_sectional`: each contraction is its own industry cross-section binned by CR4 midpoint; the three contractions are not a continuous time index. Per the project's cross-sectional handling convention:</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>- **Tolerance**: ±0.5% (cross_sectional per playbook).</t>
+          <t>- **Tolerance**: ±0.5% (cross-sectional convention).</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch8-fanout</t>
+          <t>**Author**: Anu automated extraction pipeline</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Per the playbook:</t>
+          <t>Per the same convention:</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-19T00:08:51.282845+00:00</t>
+          <t>2026-07-02T06:25:38.855377+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S802_extenbook.xlsx
+++ b/extenbooks/S802_extenbook.xlsx
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:25:38.855377+00:00</t>
+          <t>2026-07-11T03:44:26.305547+00:00</t>
         </is>
       </c>
     </row>
@@ -2157,11 +2157,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2184,6 +2184,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SEMMLER_1984_TABLE_3_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of Shaikh Figure 8.2 (Ch8, p.372). Cross-sectional: percent of industries with price increases or no decreases during each of three NBER contractions (1957-58, 1960-61, 1969-70), tabulated against CR4 concentration midpoints (20/50/80). From Weston, Lustgarten &amp; Grottke (1974) as reported in Semmler (1984, p.95). The year column (1957/1960/1969) labels each contraction's cross-section; the real explanatory axis is the CR4 midpoint. Construction-relevant: Shaikh's exhibit that the sign of the price-concentration relation flips across contractions, refuting the administered-price prediction.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S802_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S802_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cross-sectional: 3 CR4 midpoints x 3 NBER-dated contractions = 9 points. cr4_midpoint column is the disambiguator within (year, subseries_id).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
